--- a/quest_tool/tests/fixtures/items_test.xlsx
+++ b/quest_tool/tests/fixtures/items_test.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="items" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="# ItemCategory" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD25"/>
+  <dimension ref="A1:Z25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2240,4 +2241,441 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ITEM_CATEGORY_GENERAL</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>리소스 등록</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>작업이 완료된 리소스인 경우 (사운드 x)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>만료 없음</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>정의안함</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>DISPLAY_GRADE_UNSPECIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>재화</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ITEM_CATEGORY_CURRENCY</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>요청 대기</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>사운드 요청 필요한 경우</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>해당 일시에 만료</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>expire_fixed_timestamp</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>커먼</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>DISPLAY_GRADE_COMMON</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>쿠키</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ITEM_CATEGORY_COOKIE</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>요청 완료</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>사운드 요청 완료된 경우</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>N초 후 만료</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>expire_after_second</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>레어</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>DISPLAY_GRADE_RARE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>쿠키 소울칩</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ITEM_CATEGORY_COOKIE_SOUL_CHIP</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>적용 완료</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>사운드 적용 완료한 경우</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>에픽</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>DISPLAY_GRADE_EPIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>파워 샌드</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ITEM_CATEGORY_POWER_SAND</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>더미</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>더미 데이터인 경우</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>코스튬</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ITEM_CATEGORY_COSTUME</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>랜덤 아이템</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ITEM_CATEGORY_ITEM_RANDOM_POOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>아이템 상자</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ITEM_CATEGORY_ITEM_BOX</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>무료 아이템</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ITEM_CATEGORY_FREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>배틀박스</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ITEM_CATEGORY_BATTLE_BOX</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>감정표현</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ITEM_CATEGORY_EXPRESSION</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>성장 포인트</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ITEM_CATEGORY_SMASH_EXP</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>광장 아이템</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ITEM_CATEGORY_TOWN</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>프로필 아이콘</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ITEM_CATEGORY_PROFILE_ICON_ITEM</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>광고 아이템</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ITEM_CATEGORY_AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>프로필 프레임</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ITEM_CATEGORY_PROFILE_ICON_FRAME_ITEM</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>커스텀 태그</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ITEM_CATEGORY_CUSTOM_TAG_ITEM</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>칭호</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ITEM_CATEGORY_TITLE_ITEM</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>오븐 버프</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ITEM_CATEGORY_SYSTEM_BUFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>배틀 카드 포즈 아이템</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ITEM_CATEGORY_BATTLE_CARD_POSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>배틀 카드 배경 아이템</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ITEM_CATEGORY_BATTLE_CARD_BG</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>배틀 패스 포인트</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ITEM_CATEGORY_SMASH_PASS_EXP</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>아이템 그룹</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ITEM_CATEGORY_ITEM_GROUP</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>